--- a/data/trans_orig/P0901-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>153724</t>
+          <t>154128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>200432</t>
+          <t>203324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>318344</t>
+          <t>314913</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>381182</t>
+          <t>380646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>481504</t>
+          <t>488756</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>562730</t>
+          <t>571417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>831291</t>
+          <t>828399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>877999</t>
+          <t>877595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>933931</t>
+          <t>934467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>996769</t>
+          <t>1000200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1784105</t>
+          <t>1775418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1865331</t>
+          <t>1858079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76878</t>
+          <t>76760</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115419</t>
+          <t>114546</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>139135</t>
+          <t>138316</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186886</t>
+          <t>184467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>223670</t>
+          <t>226036</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>283976</t>
+          <t>284839</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1577994</t>
+          <t>1578867</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1616535</t>
+          <t>1616653</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1400787</t>
+          <t>1403206</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1448538</t>
+          <t>1449357</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2997110</t>
+          <t>2996247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3057416</t>
+          <t>3055050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16070</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>36576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31915</t>
+          <t>31925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58767</t>
+          <t>56073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53632</t>
+          <t>53349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85374</t>
+          <t>86624</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514931</t>
+          <t>514832</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535338</t>
+          <t>535554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>417645</t>
+          <t>420339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444497</t>
+          <t>444487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>942446</t>
+          <t>941196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>974188</t>
+          <t>974471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264385</t>
+          <t>264894</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>331126</t>
+          <t>336158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>507095</t>
+          <t>510656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>596362</t>
+          <t>594358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>795998</t>
+          <t>795588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>909314</t>
+          <t>900460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2945417</t>
+          <t>2940385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3012158</t>
+          <t>3011649</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2782835</t>
+          <t>2784839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2872102</t>
+          <t>2868541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5746427</t>
+          <t>5755281</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5859743</t>
+          <t>5860153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>213626</t>
+          <t>216316</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>269322</t>
+          <t>274009</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>462627</t>
+          <t>465181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>534480</t>
+          <t>538826</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>693472</t>
+          <t>700107</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>787134</t>
+          <t>790395</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,18%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>705321</t>
+          <t>700634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>761017</t>
+          <t>758327</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>803317</t>
+          <t>798971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>875170</t>
+          <t>872616</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1525306</t>
+          <t>1522045</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1618968</t>
+          <t>1612333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>117621</t>
+          <t>116827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164348</t>
+          <t>164174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>177002</t>
+          <t>174864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231977</t>
+          <t>232809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>305132</t>
+          <t>308682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382134</t>
+          <t>381413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1799609</t>
+          <t>1799783</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1846336</t>
+          <t>1847130</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1525826</t>
+          <t>1524994</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1580801</t>
+          <t>1582939</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3339626</t>
+          <t>3340347</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3416628</t>
+          <t>3413078</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,71%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43936</t>
+          <t>44555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26240</t>
+          <t>26905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50043</t>
+          <t>50983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53167</t>
+          <t>51802</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87689</t>
+          <t>86271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,18%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437245</t>
+          <t>436626</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462249</t>
+          <t>461064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>408588</t>
+          <t>407648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>432391</t>
+          <t>431726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>852124</t>
+          <t>853542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>886646</t>
+          <t>888011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>372282</t>
+          <t>374545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>450961</t>
+          <t>453130</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>694658</t>
+          <t>689232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>793403</t>
+          <t>792066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1087931</t>
+          <t>1085845</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1212123</t>
+          <t>1208330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2968821</t>
+          <t>2966652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3047500</t>
+          <t>3045237</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2760827</t>
+          <t>2762164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2859572</t>
+          <t>2864998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5761889</t>
+          <t>5765682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5886081</t>
+          <t>5888167</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>150750</t>
+          <t>151230</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198043</t>
+          <t>198601</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>340528</t>
+          <t>333932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>402153</t>
+          <t>402639</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>502412</t>
+          <t>500632</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>584659</t>
+          <t>580344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>556304</t>
+          <t>555746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603597</t>
+          <t>603117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>592507</t>
+          <t>592021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>654132</t>
+          <t>660728</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1164348</t>
+          <t>1168663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1246595</t>
+          <t>1248375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128827</t>
+          <t>124914</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>176550</t>
+          <t>175125</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>232299</t>
+          <t>231408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>295290</t>
+          <t>294273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>371561</t>
+          <t>378935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>456831</t>
+          <t>459956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1899835</t>
+          <t>1901260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1947558</t>
+          <t>1951471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1693010</t>
+          <t>1694027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1756001</t>
+          <t>1756892</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3607854</t>
+          <t>3604729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3693124</t>
+          <t>3685750</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19672</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43424</t>
+          <t>44564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42129</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72189</t>
+          <t>72767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67880</t>
+          <t>67192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109358</t>
+          <t>105478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503462</t>
+          <t>502322</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>527214</t>
+          <t>526448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>476951</t>
+          <t>476373</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>507011</t>
+          <t>507082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>986669</t>
+          <t>990549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1028147</t>
+          <t>1028835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>319653</t>
+          <t>318196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>393309</t>
+          <t>392332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>637432</t>
+          <t>634081</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>731246</t>
+          <t>738150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>984439</t>
+          <t>985365</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1112265</t>
+          <t>1106077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,01%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2984309</t>
+          <t>2985286</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3057965</t>
+          <t>3059422</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2800854</t>
+          <t>2793950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2894668</t>
+          <t>2898019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5797453</t>
+          <t>5803641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5925279</t>
+          <t>5924353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas físicos en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135790</t>
+          <t>134722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174734</t>
+          <t>173521</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>309117</t>
+          <t>308603</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>352254</t>
+          <t>352284</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>457011</t>
+          <t>456944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>515617</t>
+          <t>514256</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>340204</t>
+          <t>341417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379148</t>
+          <t>380216</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403254</t>
+          <t>403224</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446391</t>
+          <t>446905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>754829</t>
+          <t>756190</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813435</t>
+          <t>813502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>165469</t>
+          <t>177951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>287869</t>
+          <t>287960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>209961</t>
+          <t>223293</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>343830</t>
+          <t>344841</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>429461</t>
+          <t>439261</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>607182</t>
+          <t>612796</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2000294</t>
+          <t>2000203</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2122694</t>
+          <t>2110212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1892386</t>
+          <t>1891375</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2026255</t>
+          <t>2012923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3917197</t>
+          <t>3911583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4094918</t>
+          <t>4085118</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38934</t>
+          <t>39983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>67840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>51041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77566</t>
+          <t>76420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96325</t>
+          <t>96900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133099</t>
+          <t>133201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>579526</t>
+          <t>578783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>607689</t>
+          <t>606640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>582897</t>
+          <t>584043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>609060</t>
+          <t>609422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1173987</t>
+          <t>1173885</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1210761</t>
+          <t>1210186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>352156</t>
+          <t>350293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>504126</t>
+          <t>499091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>568506</t>
+          <t>580937</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>753811</t>
+          <t>760897</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>991597</t>
+          <t>996026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1227432</t>
+          <t>1228276</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2945599</t>
+          <t>2950634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3097569</t>
+          <t>3099432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2898376</t>
+          <t>2891290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3083681</t>
+          <t>3071250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5874480</t>
+          <t>5873636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6110315</t>
+          <t>6105886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0901-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P0901-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154128</t>
+          <t>155294</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>203324</t>
+          <t>204371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>314913</t>
+          <t>315556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>380646</t>
+          <t>380203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>488756</t>
+          <t>489958</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>571417</t>
+          <t>566418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>828399</t>
+          <t>827352</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>877595</t>
+          <t>876429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>934467</t>
+          <t>934910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1000200</t>
+          <t>999557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1775418</t>
+          <t>1780417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1858079</t>
+          <t>1856877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76760</t>
+          <t>78254</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114546</t>
+          <t>115584</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138316</t>
+          <t>135870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184467</t>
+          <t>186923</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>226036</t>
+          <t>226409</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>284839</t>
+          <t>287520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1578867</t>
+          <t>1577829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1616653</t>
+          <t>1615159</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1403206</t>
+          <t>1400750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1449357</t>
+          <t>1451803</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2996247</t>
+          <t>2993566</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3055050</t>
+          <t>3054677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15854</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36576</t>
+          <t>36919</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>31357</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56073</t>
+          <t>57903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53349</t>
+          <t>53605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86624</t>
+          <t>85870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514832</t>
+          <t>514489</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535554</t>
+          <t>534872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>420339</t>
+          <t>418509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444487</t>
+          <t>445055</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>941196</t>
+          <t>941950</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>974471</t>
+          <t>974215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264894</t>
+          <t>266224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>336158</t>
+          <t>332220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>510656</t>
+          <t>509670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>594358</t>
+          <t>596973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>795588</t>
+          <t>795572</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>900460</t>
+          <t>901563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2940385</t>
+          <t>2944323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3011649</t>
+          <t>3010319</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2784839</t>
+          <t>2782224</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2868541</t>
+          <t>2869527</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5755281</t>
+          <t>5754178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5860153</t>
+          <t>5860169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>216316</t>
+          <t>214514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>274009</t>
+          <t>273270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>465181</t>
+          <t>464923</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>538826</t>
+          <t>536256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>700107</t>
+          <t>692952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>790395</t>
+          <t>787658</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>700634</t>
+          <t>701373</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>758327</t>
+          <t>760129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>798971</t>
+          <t>801541</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>872616</t>
+          <t>872874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1522045</t>
+          <t>1524782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1612333</t>
+          <t>1619488</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>70,03%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>116827</t>
+          <t>116743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>164174</t>
+          <t>161864</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174864</t>
+          <t>179596</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>232809</t>
+          <t>236097</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>308682</t>
+          <t>308084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>381413</t>
+          <t>382813</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1799783</t>
+          <t>1802093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1847130</t>
+          <t>1847214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1524994</t>
+          <t>1521706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1582939</t>
+          <t>1578207</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3340347</t>
+          <t>3338947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3413078</t>
+          <t>3413676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44555</t>
+          <t>44560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26905</t>
+          <t>24740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50983</t>
+          <t>50025</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51802</t>
+          <t>52679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86271</t>
+          <t>87083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436626</t>
+          <t>436621</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>461064</t>
+          <t>460326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>407648</t>
+          <t>408606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>431726</t>
+          <t>433891</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>853542</t>
+          <t>852730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>888011</t>
+          <t>887134</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>374545</t>
+          <t>371617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>453130</t>
+          <t>453255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>689232</t>
+          <t>694043</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>792066</t>
+          <t>789437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1085845</t>
+          <t>1087097</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1208330</t>
+          <t>1214532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2966652</t>
+          <t>2966527</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3045237</t>
+          <t>3048165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2762164</t>
+          <t>2764793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2864998</t>
+          <t>2860187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5765682</t>
+          <t>5759480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5888167</t>
+          <t>5886915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>151230</t>
+          <t>153943</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198601</t>
+          <t>197563</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>333932</t>
+          <t>334166</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>402639</t>
+          <t>398693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>500632</t>
+          <t>500721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>580344</t>
+          <t>580375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>555746</t>
+          <t>556784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603117</t>
+          <t>600404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>592021</t>
+          <t>595967</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>660728</t>
+          <t>660494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1168663</t>
+          <t>1168632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1248375</t>
+          <t>1248286</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124914</t>
+          <t>128115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>175125</t>
+          <t>176197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>231408</t>
+          <t>234014</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>294273</t>
+          <t>297713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>378935</t>
+          <t>372765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>459956</t>
+          <t>454835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1901260</t>
+          <t>1900188</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1951471</t>
+          <t>1948270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1694027</t>
+          <t>1690587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1756892</t>
+          <t>1754286</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3604729</t>
+          <t>3609850</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3685750</t>
+          <t>3691920</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>19281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44564</t>
+          <t>43506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>41864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72767</t>
+          <t>70660</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67192</t>
+          <t>66493</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105478</t>
+          <t>103594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502322</t>
+          <t>503380</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>526448</t>
+          <t>527605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>476373</t>
+          <t>478480</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>507082</t>
+          <t>507276</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>990549</t>
+          <t>992433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1028835</t>
+          <t>1029534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>318196</t>
+          <t>319082</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>392332</t>
+          <t>394421</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>634081</t>
+          <t>641534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>738150</t>
+          <t>742345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>985365</t>
+          <t>981420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1106077</t>
+          <t>1103965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2985286</t>
+          <t>2983197</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3059422</t>
+          <t>3058536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2793950</t>
+          <t>2789755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2898019</t>
+          <t>2890566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5803641</t>
+          <t>5805753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5924353</t>
+          <t>5928298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>153717</t>
+          <t>164617</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134722</t>
+          <t>145016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173521</t>
+          <t>186016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>330965</t>
+          <t>355578</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>308603</t>
+          <t>333167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>352284</t>
+          <t>378863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>484683</t>
+          <t>520195</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>456944</t>
+          <t>487643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>514256</t>
+          <t>551178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>39,35%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>361221</t>
+          <t>413912</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>341417</t>
+          <t>392513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>380216</t>
+          <t>433513</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>424543</t>
+          <t>466460</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403224</t>
+          <t>443175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>446905</t>
+          <t>488871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>785763</t>
+          <t>880372</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>756190</t>
+          <t>849389</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813502</t>
+          <t>912924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>65,18%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>244005</t>
+          <t>261791</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>177951</t>
+          <t>231163</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>287960</t>
+          <t>296148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>298337</t>
+          <t>338134</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>223293</t>
+          <t>310037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>344841</t>
+          <t>368902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>542342</t>
+          <t>599926</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>439261</t>
+          <t>554241</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>612796</t>
+          <t>647662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2044158</t>
+          <t>1966592</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2000203</t>
+          <t>1932235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2110212</t>
+          <t>1997220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1937879</t>
+          <t>1831569</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1891375</t>
+          <t>1800801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2012923</t>
+          <t>1859666</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3982037</t>
+          <t>3798161</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3911583</t>
+          <t>3750425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4085118</t>
+          <t>3843846</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2288163</t>
+          <t>2228383</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2288163</t>
+          <t>2228383</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2288163</t>
+          <t>2228383</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2236216</t>
+          <t>2169703</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2236216</t>
+          <t>2169703</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2236216</t>
+          <t>2169703</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4524379</t>
+          <t>4398087</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4524379</t>
+          <t>4398087</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524379</t>
+          <t>4398087</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50997</t>
+          <t>54594</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39983</t>
+          <t>41026</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67840</t>
+          <t>71524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>63181</t>
+          <t>76432</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51041</t>
+          <t>63039</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76420</t>
+          <t>91055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>114178</t>
+          <t>131027</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96900</t>
+          <t>111295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133201</t>
+          <t>153257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>595626</t>
+          <t>656993</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>578783</t>
+          <t>640063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606640</t>
+          <t>670561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>597282</t>
+          <t>658445</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>584043</t>
+          <t>643822</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>609422</t>
+          <t>671838</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1192908</t>
+          <t>1315437</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1173885</t>
+          <t>1293207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1210186</t>
+          <t>1335169</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>448720</t>
+          <t>481003</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>350293</t>
+          <t>438477</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>499091</t>
+          <t>522035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>692484</t>
+          <t>770145</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>580937</t>
+          <t>729379</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>760897</t>
+          <t>809418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1141203</t>
+          <t>1251147</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>996026</t>
+          <t>1193553</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1228276</t>
+          <t>1308922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3001005</t>
+          <t>3037497</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2950634</t>
+          <t>2996465</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3099432</t>
+          <t>3080023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2959703</t>
+          <t>2956473</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2891290</t>
+          <t>2917200</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3071250</t>
+          <t>2997239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5960709</t>
+          <t>5993971</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5873636</t>
+          <t>5936196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6105886</t>
+          <t>6051565</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3449725</t>
+          <t>3518500</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3449725</t>
+          <t>3518500</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3449725</t>
+          <t>3518500</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3652187</t>
+          <t>3726618</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3652187</t>
+          <t>3726618</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3652187</t>
+          <t>3726618</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7101912</t>
+          <t>7245118</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7101912</t>
+          <t>7245118</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7101912</t>
+          <t>7245118</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
